--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,1464 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123361790</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>506921</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6992561</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123361789</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>506918</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6992555</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123361786</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>506816</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6992606</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123361784</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>506806</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6992719</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123361792</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>506764</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6992754</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123361788</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>507086</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6992321</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123361785</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>506757</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6992768</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123361782</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>506875</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6992618</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123361780</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>506956</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6992441</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123361778</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>506992</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6992277</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123361779</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>506956</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6992433</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123361783</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>506764</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6992771</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123361781</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>506927</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6992503</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123361793</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>506759</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6992756</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361790</v>
+        <v>123361789</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506921</v>
+        <v>506918</v>
       </c>
       <c r="R3" t="n">
-        <v>6992561</v>
+        <v>6992555</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123361789</v>
+        <v>123361779</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506918</v>
+        <v>506956</v>
       </c>
       <c r="R4" t="n">
-        <v>6992555</v>
+        <v>6992433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,6 +969,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123361786</v>
+        <v>123361788</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506816</v>
+        <v>507086</v>
       </c>
       <c r="R5" t="n">
-        <v>6992606</v>
+        <v>6992321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123361784</v>
+        <v>123361778</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1118,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506806</v>
+        <v>506992</v>
       </c>
       <c r="R6" t="n">
-        <v>6992719</v>
+        <v>6992277</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,6 +1178,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123361792</v>
+        <v>123361784</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506764</v>
+        <v>506806</v>
       </c>
       <c r="R7" t="n">
-        <v>6992754</v>
+        <v>6992719</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123361788</v>
+        <v>123361786</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507086</v>
+        <v>506816</v>
       </c>
       <c r="R8" t="n">
-        <v>6992321</v>
+        <v>6992606</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123361785</v>
+        <v>123361792</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506757</v>
+        <v>506764</v>
       </c>
       <c r="R9" t="n">
-        <v>6992768</v>
+        <v>6992754</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361782</v>
+        <v>123361780</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506875</v>
+        <v>506956</v>
       </c>
       <c r="R10" t="n">
-        <v>6992618</v>
+        <v>6992441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123361780</v>
+        <v>123361781</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506956</v>
+        <v>506927</v>
       </c>
       <c r="R11" t="n">
-        <v>6992441</v>
+        <v>6992503</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1692,7 +1702,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123361778</v>
+        <v>123361783</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506992</v>
+        <v>506764</v>
       </c>
       <c r="R12" t="n">
-        <v>6992277</v>
+        <v>6992771</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1809,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123361779</v>
+        <v>123361785</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506956</v>
+        <v>506757</v>
       </c>
       <c r="R13" t="n">
-        <v>6992433</v>
+        <v>6992768</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,11 +1912,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1933,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361783</v>
+        <v>123361790</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,21 +1954,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506764</v>
+        <v>506921</v>
       </c>
       <c r="R14" t="n">
-        <v>6992771</v>
+        <v>6992561</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,11 +2014,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,10 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123361781</v>
+        <v>123361793</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506927</v>
+        <v>506759</v>
       </c>
       <c r="R15" t="n">
-        <v>6992503</v>
+        <v>6992756</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,11 +2116,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2147,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123361793</v>
+        <v>123361782</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2163,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2187,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506759</v>
+        <v>506875</v>
       </c>
       <c r="R16" t="n">
-        <v>6992756</v>
+        <v>6992618</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,6 +2218,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361789</v>
+        <v>123361790</v>
       </c>
       <c r="B3" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506918</v>
+        <v>506921</v>
       </c>
       <c r="R3" t="n">
-        <v>6992555</v>
+        <v>6992561</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123361779</v>
+        <v>123361784</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506956</v>
+        <v>506806</v>
       </c>
       <c r="R4" t="n">
-        <v>6992433</v>
+        <v>6992719</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,11 +969,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +998,7 @@
         <v>123361788</v>
       </c>
       <c r="B5" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1102,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123361778</v>
+        <v>123361789</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506992</v>
+        <v>506918</v>
       </c>
       <c r="R6" t="n">
-        <v>6992277</v>
+        <v>6992555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,11 +1173,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123361784</v>
+        <v>123361779</v>
       </c>
       <c r="B7" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,21 +1215,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506806</v>
+        <v>506956</v>
       </c>
       <c r="R7" t="n">
-        <v>6992719</v>
+        <v>6992433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,6 +1275,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123361786</v>
+        <v>123361781</v>
       </c>
       <c r="B8" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506816</v>
+        <v>506927</v>
       </c>
       <c r="R8" t="n">
-        <v>6992606</v>
+        <v>6992503</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,6 +1382,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123361792</v>
+        <v>123361780</v>
       </c>
       <c r="B9" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506764</v>
+        <v>506956</v>
       </c>
       <c r="R9" t="n">
-        <v>6992754</v>
+        <v>6992441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,6 +1489,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,7 +1520,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361780</v>
+        <v>123361783</v>
       </c>
       <c r="B10" t="n">
         <v>57481</v>
@@ -1555,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506956</v>
+        <v>506764</v>
       </c>
       <c r="R10" t="n">
-        <v>6992441</v>
+        <v>6992771</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1600,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123361781</v>
+        <v>123361786</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,21 +1643,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506927</v>
+        <v>506816</v>
       </c>
       <c r="R11" t="n">
-        <v>6992503</v>
+        <v>6992606</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,11 +1703,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1729,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123361783</v>
+        <v>123361785</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,21 +1745,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506764</v>
+        <v>506757</v>
       </c>
       <c r="R12" t="n">
-        <v>6992771</v>
+        <v>6992768</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,11 +1805,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1836,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123361785</v>
+        <v>123361782</v>
       </c>
       <c r="B13" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1852,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506757</v>
+        <v>506875</v>
       </c>
       <c r="R13" t="n">
-        <v>6992768</v>
+        <v>6992618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,6 +1907,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1938,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361790</v>
+        <v>123361792</v>
       </c>
       <c r="B14" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506921</v>
+        <v>506764</v>
       </c>
       <c r="R14" t="n">
-        <v>6992561</v>
+        <v>6992754</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123361793</v>
+        <v>123361778</v>
       </c>
       <c r="B15" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506759</v>
+        <v>506992</v>
       </c>
       <c r="R15" t="n">
-        <v>6992756</v>
+        <v>6992277</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,6 +2116,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123361782</v>
+        <v>123361793</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,21 +2163,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2182,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506875</v>
+        <v>506759</v>
       </c>
       <c r="R16" t="n">
-        <v>6992618</v>
+        <v>6992756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,11 +2223,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361790</v>
+        <v>123361793</v>
       </c>
       <c r="B3" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506921</v>
+        <v>506759</v>
       </c>
       <c r="R3" t="n">
-        <v>6992561</v>
+        <v>6992756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123361784</v>
+        <v>123361778</v>
       </c>
       <c r="B4" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506806</v>
+        <v>506992</v>
       </c>
       <c r="R4" t="n">
-        <v>6992719</v>
+        <v>6992277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,6 +969,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123361788</v>
+        <v>123361779</v>
       </c>
       <c r="B5" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507086</v>
+        <v>506956</v>
       </c>
       <c r="R5" t="n">
-        <v>6992321</v>
+        <v>6992433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,6 +1076,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123361789</v>
+        <v>123361780</v>
       </c>
       <c r="B6" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506918</v>
+        <v>506956</v>
       </c>
       <c r="R6" t="n">
-        <v>6992555</v>
+        <v>6992441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,6 +1183,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123361779</v>
+        <v>123361790</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1230,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506956</v>
+        <v>506921</v>
       </c>
       <c r="R7" t="n">
-        <v>6992433</v>
+        <v>6992561</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,11 +1290,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123361781</v>
+        <v>123361792</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506927</v>
+        <v>506764</v>
       </c>
       <c r="R8" t="n">
-        <v>6992503</v>
+        <v>6992754</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123361780</v>
+        <v>123361781</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1453,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506956</v>
+        <v>506927</v>
       </c>
       <c r="R9" t="n">
-        <v>6992441</v>
+        <v>6992503</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,7 +1498,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361783</v>
+        <v>123361789</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,21 +1541,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506764</v>
+        <v>506918</v>
       </c>
       <c r="R10" t="n">
-        <v>6992771</v>
+        <v>6992555</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,11 +1601,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123361786</v>
+        <v>123361785</v>
       </c>
       <c r="B11" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506816</v>
+        <v>506757</v>
       </c>
       <c r="R11" t="n">
-        <v>6992606</v>
+        <v>6992768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123361785</v>
+        <v>123361788</v>
       </c>
       <c r="B12" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506757</v>
+        <v>507086</v>
       </c>
       <c r="R12" t="n">
-        <v>6992768</v>
+        <v>6992321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361792</v>
+        <v>123361786</v>
       </c>
       <c r="B14" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506764</v>
+        <v>506816</v>
       </c>
       <c r="R14" t="n">
-        <v>6992754</v>
+        <v>6992606</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123361778</v>
+        <v>123361783</v>
       </c>
       <c r="B15" t="n">
         <v>57481</v>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506992</v>
+        <v>506764</v>
       </c>
       <c r="R15" t="n">
-        <v>6992277</v>
+        <v>6992771</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2147,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123361793</v>
+        <v>123361784</v>
       </c>
       <c r="B16" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506759</v>
+        <v>506806</v>
       </c>
       <c r="R16" t="n">
-        <v>6992756</v>
+        <v>6992719</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361786</v>
+        <v>123361785</v>
       </c>
       <c r="B3" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506816</v>
+        <v>506757</v>
       </c>
       <c r="R3" t="n">
-        <v>6992606</v>
+        <v>6992768</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +896,7 @@
         <v>123361784</v>
       </c>
       <c r="B4" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123361790</v>
+        <v>123361786</v>
       </c>
       <c r="B5" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506921</v>
+        <v>506816</v>
       </c>
       <c r="R5" t="n">
-        <v>6992561</v>
+        <v>6992606</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123361793</v>
+        <v>123361780</v>
       </c>
       <c r="B6" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506759</v>
+        <v>506956</v>
       </c>
       <c r="R6" t="n">
-        <v>6992756</v>
+        <v>6992441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,6 +1173,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,7 +1207,7 @@
         <v>123361792</v>
       </c>
       <c r="B7" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123361785</v>
+        <v>123361778</v>
       </c>
       <c r="B8" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506757</v>
+        <v>506992</v>
       </c>
       <c r="R8" t="n">
-        <v>6992768</v>
+        <v>6992277</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,6 +1382,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123361789</v>
+        <v>123361788</v>
       </c>
       <c r="B9" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506918</v>
+        <v>507086</v>
       </c>
       <c r="R9" t="n">
-        <v>6992555</v>
+        <v>6992321</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361783</v>
+        <v>123361793</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,21 +1531,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506764</v>
+        <v>506759</v>
       </c>
       <c r="R10" t="n">
-        <v>6992771</v>
+        <v>6992756</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,11 +1591,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123361781</v>
+        <v>123361783</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1652,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506927</v>
+        <v>506764</v>
       </c>
       <c r="R11" t="n">
-        <v>6992503</v>
+        <v>6992771</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123361779</v>
+        <v>123361790</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,21 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506956</v>
+        <v>506921</v>
       </c>
       <c r="R12" t="n">
-        <v>6992433</v>
+        <v>6992561</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,11 +1800,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123361778</v>
+        <v>123361782</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506992</v>
+        <v>506875</v>
       </c>
       <c r="R13" t="n">
-        <v>6992277</v>
+        <v>6992618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1933,10 +1933,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361780</v>
+        <v>123361789</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506956</v>
+        <v>506918</v>
       </c>
       <c r="R14" t="n">
-        <v>6992441</v>
+        <v>6992555</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,11 +2009,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,10 +2035,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123361788</v>
+        <v>123361779</v>
       </c>
       <c r="B15" t="n">
-        <v>79856</v>
+        <v>57487</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,21 +2051,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2080,10 +2075,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507086</v>
+        <v>506956</v>
       </c>
       <c r="R15" t="n">
-        <v>6992321</v>
+        <v>6992433</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,6 +2111,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123361782</v>
+        <v>123361781</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506875</v>
+        <v>506927</v>
       </c>
       <c r="R16" t="n">
-        <v>6992618</v>
+        <v>6992503</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361785</v>
+        <v>123361793</v>
       </c>
       <c r="B3" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506757</v>
+        <v>506759</v>
       </c>
       <c r="R3" t="n">
-        <v>6992768</v>
+        <v>6992756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123361784</v>
+        <v>123361779</v>
       </c>
       <c r="B4" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506806</v>
+        <v>506956</v>
       </c>
       <c r="R4" t="n">
-        <v>6992719</v>
+        <v>6992433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,6 +969,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123361786</v>
+        <v>123361788</v>
       </c>
       <c r="B5" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506816</v>
+        <v>507086</v>
       </c>
       <c r="R5" t="n">
-        <v>6992606</v>
+        <v>6992321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1105,7 @@
         <v>123361780</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1204,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123361792</v>
+        <v>123361790</v>
       </c>
       <c r="B7" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506764</v>
+        <v>506921</v>
       </c>
       <c r="R7" t="n">
-        <v>6992754</v>
+        <v>6992561</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123361778</v>
+        <v>123361786</v>
       </c>
       <c r="B8" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506992</v>
+        <v>506816</v>
       </c>
       <c r="R8" t="n">
-        <v>6992277</v>
+        <v>6992606</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,11 +1387,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123361788</v>
+        <v>123361792</v>
       </c>
       <c r="B9" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507086</v>
+        <v>506764</v>
       </c>
       <c r="R9" t="n">
-        <v>6992321</v>
+        <v>6992754</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361793</v>
+        <v>123361778</v>
       </c>
       <c r="B10" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,21 +1531,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506759</v>
+        <v>506992</v>
       </c>
       <c r="R10" t="n">
-        <v>6992756</v>
+        <v>6992277</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,6 +1591,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123361783</v>
+        <v>123361785</v>
       </c>
       <c r="B11" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,21 +1638,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506764</v>
+        <v>506757</v>
       </c>
       <c r="R11" t="n">
-        <v>6992771</v>
+        <v>6992768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,11 +1698,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123361790</v>
+        <v>123361783</v>
       </c>
       <c r="B12" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,21 +1740,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506921</v>
+        <v>506764</v>
       </c>
       <c r="R12" t="n">
-        <v>6992561</v>
+        <v>6992771</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,6 +1800,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1829,7 +1834,7 @@
         <v>123361782</v>
       </c>
       <c r="B13" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361789</v>
+        <v>123361784</v>
       </c>
       <c r="B14" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506918</v>
+        <v>506806</v>
       </c>
       <c r="R14" t="n">
-        <v>6992555</v>
+        <v>6992719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,10 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123361779</v>
+        <v>123361789</v>
       </c>
       <c r="B15" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,21 +2056,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2075,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506956</v>
+        <v>506918</v>
       </c>
       <c r="R15" t="n">
-        <v>6992433</v>
+        <v>6992555</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,11 +2116,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2145,7 +2145,7 @@
         <v>123361781</v>
       </c>
       <c r="B16" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361793</v>
+        <v>123361789</v>
       </c>
       <c r="B3" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506759</v>
+        <v>506918</v>
       </c>
       <c r="R3" t="n">
-        <v>6992756</v>
+        <v>6992555</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123361779</v>
+        <v>123361784</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506956</v>
+        <v>506806</v>
       </c>
       <c r="R4" t="n">
-        <v>6992433</v>
+        <v>6992719</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,11 +969,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123361788</v>
+        <v>123361792</v>
       </c>
       <c r="B5" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507086</v>
+        <v>506764</v>
       </c>
       <c r="R5" t="n">
-        <v>6992321</v>
+        <v>6992754</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1100,7 @@
         <v>123361780</v>
       </c>
       <c r="B6" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1209,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123361790</v>
+        <v>123361788</v>
       </c>
       <c r="B7" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506921</v>
+        <v>507086</v>
       </c>
       <c r="R7" t="n">
-        <v>6992561</v>
+        <v>6992321</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1309,7 @@
         <v>123361786</v>
       </c>
       <c r="B8" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123361792</v>
+        <v>123361783</v>
       </c>
       <c r="B9" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,21 +1424,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1456,7 +1451,7 @@
         <v>506764</v>
       </c>
       <c r="R9" t="n">
-        <v>6992754</v>
+        <v>6992771</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,6 +1484,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361778</v>
+        <v>123361779</v>
       </c>
       <c r="B10" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506992</v>
+        <v>506956</v>
       </c>
       <c r="R10" t="n">
-        <v>6992277</v>
+        <v>6992433</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123361785</v>
+        <v>123361778</v>
       </c>
       <c r="B11" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,21 +1638,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506757</v>
+        <v>506992</v>
       </c>
       <c r="R11" t="n">
-        <v>6992768</v>
+        <v>6992277</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,6 +1698,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123361783</v>
+        <v>123361785</v>
       </c>
       <c r="B12" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,21 +1745,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1764,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506764</v>
+        <v>506757</v>
       </c>
       <c r="R12" t="n">
-        <v>6992771</v>
+        <v>6992768</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,11 +1805,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1831,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123361782</v>
+        <v>123361793</v>
       </c>
       <c r="B13" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506875</v>
+        <v>506759</v>
       </c>
       <c r="R13" t="n">
-        <v>6992618</v>
+        <v>6992756</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,11 +1907,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1938,10 +1933,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361784</v>
+        <v>123361782</v>
       </c>
       <c r="B14" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1978,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506806</v>
+        <v>506875</v>
       </c>
       <c r="R14" t="n">
-        <v>6992719</v>
+        <v>6992618</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,6 +2009,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2040,10 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123361789</v>
+        <v>123361790</v>
       </c>
       <c r="B15" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506918</v>
+        <v>506921</v>
       </c>
       <c r="R15" t="n">
-        <v>6992555</v>
+        <v>6992561</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
         <v>123361781</v>
       </c>
       <c r="B16" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -1831,10 +1831,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123361793</v>
+        <v>123361782</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506759</v>
+        <v>506875</v>
       </c>
       <c r="R13" t="n">
-        <v>6992756</v>
+        <v>6992618</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,6 +1907,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1933,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361782</v>
+        <v>123361793</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,21 +1954,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506875</v>
+        <v>506759</v>
       </c>
       <c r="R14" t="n">
-        <v>6992618</v>
+        <v>6992756</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,11 +2014,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361789</v>
+        <v>123361786</v>
       </c>
       <c r="B3" t="n">
         <v>79869</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506918</v>
+        <v>506816</v>
       </c>
       <c r="R3" t="n">
-        <v>6992555</v>
+        <v>6992606</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123361784</v>
+        <v>123361793</v>
       </c>
       <c r="B4" t="n">
         <v>79869</v>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506806</v>
+        <v>506759</v>
       </c>
       <c r="R4" t="n">
-        <v>6992719</v>
+        <v>6992756</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123361780</v>
+        <v>123361781</v>
       </c>
       <c r="B6" t="n">
         <v>57491</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506956</v>
+        <v>506927</v>
       </c>
       <c r="R6" t="n">
-        <v>6992441</v>
+        <v>6992503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123361788</v>
+        <v>123361780</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507086</v>
+        <v>506956</v>
       </c>
       <c r="R7" t="n">
-        <v>6992321</v>
+        <v>6992441</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,6 +1280,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123361786</v>
+        <v>123361783</v>
       </c>
       <c r="B8" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506816</v>
+        <v>506764</v>
       </c>
       <c r="R8" t="n">
-        <v>6992606</v>
+        <v>6992771</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,6 +1387,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123361783</v>
+        <v>123361789</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506764</v>
+        <v>506918</v>
       </c>
       <c r="R9" t="n">
-        <v>6992771</v>
+        <v>6992555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,11 +1494,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361779</v>
+        <v>123361788</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,21 +1536,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506956</v>
+        <v>507086</v>
       </c>
       <c r="R10" t="n">
-        <v>6992433</v>
+        <v>6992321</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,11 +1596,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,7 +1729,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123361785</v>
+        <v>123361790</v>
       </c>
       <c r="B12" t="n">
         <v>79869</v>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506757</v>
+        <v>506921</v>
       </c>
       <c r="R12" t="n">
-        <v>6992768</v>
+        <v>6992561</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361793</v>
+        <v>123361784</v>
       </c>
       <c r="B14" t="n">
         <v>79869</v>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506759</v>
+        <v>506806</v>
       </c>
       <c r="R14" t="n">
-        <v>6992756</v>
+        <v>6992719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123361790</v>
+        <v>123361785</v>
       </c>
       <c r="B15" t="n">
         <v>79869</v>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506921</v>
+        <v>506757</v>
       </c>
       <c r="R15" t="n">
-        <v>6992561</v>
+        <v>6992768</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123361781</v>
+        <v>123361779</v>
       </c>
       <c r="B16" t="n">
         <v>57491</v>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506927</v>
+        <v>506956</v>
       </c>
       <c r="R16" t="n">
-        <v>6992503</v>
+        <v>6992433</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -1418,7 +1418,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123361789</v>
+        <v>123361788</v>
       </c>
       <c r="B9" t="n">
         <v>79869</v>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506918</v>
+        <v>507086</v>
       </c>
       <c r="R9" t="n">
-        <v>6992555</v>
+        <v>6992321</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1520,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361788</v>
+        <v>123361789</v>
       </c>
       <c r="B10" t="n">
         <v>79869</v>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507086</v>
+        <v>506918</v>
       </c>
       <c r="R10" t="n">
-        <v>6992321</v>
+        <v>6992555</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361786</v>
+        <v>123361779</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506816</v>
+        <v>506956</v>
       </c>
       <c r="R3" t="n">
-        <v>6992606</v>
+        <v>6992433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123361793</v>
+        <v>123361778</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506759</v>
+        <v>506992</v>
       </c>
       <c r="R4" t="n">
-        <v>6992756</v>
+        <v>6992277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,6 +974,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123361792</v>
+        <v>123361780</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506764</v>
+        <v>506956</v>
       </c>
       <c r="R5" t="n">
-        <v>6992754</v>
+        <v>6992441</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,6 +1081,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123361781</v>
+        <v>123361784</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506927</v>
+        <v>506806</v>
       </c>
       <c r="R6" t="n">
-        <v>6992503</v>
+        <v>6992719</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,11 +1188,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123361780</v>
+        <v>123361792</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,21 +1230,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1244,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506956</v>
+        <v>506764</v>
       </c>
       <c r="R7" t="n">
-        <v>6992441</v>
+        <v>6992754</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,11 +1290,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123361783</v>
+        <v>123361785</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506764</v>
+        <v>506757</v>
       </c>
       <c r="R8" t="n">
-        <v>6992771</v>
+        <v>6992768</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,11 +1392,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,7 +1520,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361789</v>
+        <v>123361793</v>
       </c>
       <c r="B10" t="n">
         <v>79869</v>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506918</v>
+        <v>506759</v>
       </c>
       <c r="R10" t="n">
-        <v>6992555</v>
+        <v>6992756</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123361778</v>
+        <v>123361781</v>
       </c>
       <c r="B11" t="n">
         <v>57491</v>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506992</v>
+        <v>506927</v>
       </c>
       <c r="R11" t="n">
-        <v>6992277</v>
+        <v>6992503</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1831,7 +1831,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123361782</v>
+        <v>123361783</v>
       </c>
       <c r="B13" t="n">
         <v>57491</v>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506875</v>
+        <v>506764</v>
       </c>
       <c r="R13" t="n">
-        <v>6992618</v>
+        <v>6992771</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1938,7 +1938,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361784</v>
+        <v>123361789</v>
       </c>
       <c r="B14" t="n">
         <v>79869</v>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506806</v>
+        <v>506918</v>
       </c>
       <c r="R14" t="n">
-        <v>6992719</v>
+        <v>6992555</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123361785</v>
+        <v>123361786</v>
       </c>
       <c r="B15" t="n">
         <v>79869</v>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506757</v>
+        <v>506816</v>
       </c>
       <c r="R15" t="n">
-        <v>6992768</v>
+        <v>6992606</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2142,7 +2142,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123361779</v>
+        <v>123361782</v>
       </c>
       <c r="B16" t="n">
         <v>57491</v>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506956</v>
+        <v>506875</v>
       </c>
       <c r="R16" t="n">
-        <v>6992433</v>
+        <v>6992618</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361779</v>
+        <v>123361780</v>
       </c>
       <c r="B3" t="n">
         <v>57491</v>
@@ -834,7 +834,7 @@
         <v>506956</v>
       </c>
       <c r="R3" t="n">
-        <v>6992433</v>
+        <v>6992441</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123361778</v>
+        <v>123361790</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506992</v>
+        <v>506921</v>
       </c>
       <c r="R4" t="n">
-        <v>6992277</v>
+        <v>6992561</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,11 +974,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123361780</v>
+        <v>123361788</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506956</v>
+        <v>507086</v>
       </c>
       <c r="R5" t="n">
-        <v>6992441</v>
+        <v>6992321</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,11 +1076,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123361784</v>
+        <v>123361793</v>
       </c>
       <c r="B6" t="n">
         <v>79869</v>
@@ -1152,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506806</v>
+        <v>506759</v>
       </c>
       <c r="R6" t="n">
-        <v>6992719</v>
+        <v>6992756</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123361792</v>
+        <v>123361782</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506764</v>
+        <v>506875</v>
       </c>
       <c r="R7" t="n">
-        <v>6992754</v>
+        <v>6992618</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,6 +1280,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123361785</v>
+        <v>123361789</v>
       </c>
       <c r="B8" t="n">
         <v>79869</v>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506757</v>
+        <v>506918</v>
       </c>
       <c r="R8" t="n">
-        <v>6992768</v>
+        <v>6992555</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123361788</v>
+        <v>123361778</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,21 +1429,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1458,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507086</v>
+        <v>506992</v>
       </c>
       <c r="R9" t="n">
-        <v>6992321</v>
+        <v>6992277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,6 +1489,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361793</v>
+        <v>123361781</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,21 +1536,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506759</v>
+        <v>506927</v>
       </c>
       <c r="R10" t="n">
-        <v>6992756</v>
+        <v>6992503</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,6 +1596,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123361781</v>
+        <v>123361785</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,21 +1643,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506927</v>
+        <v>506757</v>
       </c>
       <c r="R11" t="n">
-        <v>6992503</v>
+        <v>6992768</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,11 +1703,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1729,7 +1729,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123361790</v>
+        <v>123361792</v>
       </c>
       <c r="B12" t="n">
         <v>79869</v>
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506921</v>
+        <v>506764</v>
       </c>
       <c r="R12" t="n">
-        <v>6992561</v>
+        <v>6992754</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361789</v>
+        <v>123361784</v>
       </c>
       <c r="B14" t="n">
         <v>79869</v>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506918</v>
+        <v>506806</v>
       </c>
       <c r="R14" t="n">
-        <v>6992555</v>
+        <v>6992719</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,10 +2040,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123361786</v>
+        <v>123361779</v>
       </c>
       <c r="B15" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,21 +2056,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506816</v>
+        <v>506956</v>
       </c>
       <c r="R15" t="n">
-        <v>6992606</v>
+        <v>6992433</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2116,6 +2116,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123361782</v>
+        <v>123361786</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,21 +2163,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2182,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506875</v>
+        <v>506816</v>
       </c>
       <c r="R16" t="n">
-        <v>6992618</v>
+        <v>6992606</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,11 +2223,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361780</v>
+        <v>123361792</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506956</v>
+        <v>506764</v>
       </c>
       <c r="R3" t="n">
-        <v>6992441</v>
+        <v>6992754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,11 +867,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +893,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123361790</v>
+        <v>123361788</v>
       </c>
       <c r="B4" t="n">
         <v>79869</v>
@@ -938,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506921</v>
+        <v>507086</v>
       </c>
       <c r="R4" t="n">
-        <v>6992561</v>
+        <v>6992321</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +995,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123361788</v>
+        <v>123361793</v>
       </c>
       <c r="B5" t="n">
         <v>79869</v>
@@ -1040,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507086</v>
+        <v>506759</v>
       </c>
       <c r="R5" t="n">
-        <v>6992321</v>
+        <v>6992756</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123361793</v>
+        <v>123361780</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506759</v>
+        <v>506956</v>
       </c>
       <c r="R6" t="n">
-        <v>6992756</v>
+        <v>6992441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,6 +1173,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,7 +1204,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123361782</v>
+        <v>123361778</v>
       </c>
       <c r="B7" t="n">
         <v>57491</v>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506875</v>
+        <v>506992</v>
       </c>
       <c r="R7" t="n">
-        <v>6992618</v>
+        <v>6992277</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123361789</v>
+        <v>123361784</v>
       </c>
       <c r="B8" t="n">
         <v>79869</v>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506918</v>
+        <v>506806</v>
       </c>
       <c r="R8" t="n">
-        <v>6992555</v>
+        <v>6992719</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,7 +1413,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123361778</v>
+        <v>123361783</v>
       </c>
       <c r="B9" t="n">
         <v>57491</v>
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506992</v>
+        <v>506764</v>
       </c>
       <c r="R9" t="n">
-        <v>6992277</v>
+        <v>6992771</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361781</v>
+        <v>123361785</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,21 +1536,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506927</v>
+        <v>506757</v>
       </c>
       <c r="R10" t="n">
-        <v>6992503</v>
+        <v>6992768</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,11 +1596,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,7 +1622,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123361785</v>
+        <v>123361789</v>
       </c>
       <c r="B11" t="n">
         <v>79869</v>
@@ -1667,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506757</v>
+        <v>506918</v>
       </c>
       <c r="R11" t="n">
-        <v>6992768</v>
+        <v>6992555</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1724,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123361792</v>
+        <v>123361790</v>
       </c>
       <c r="B12" t="n">
         <v>79869</v>
@@ -1769,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506764</v>
+        <v>506921</v>
       </c>
       <c r="R12" t="n">
-        <v>6992754</v>
+        <v>6992561</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123361783</v>
+        <v>123361786</v>
       </c>
       <c r="B13" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,21 +1842,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506764</v>
+        <v>506816</v>
       </c>
       <c r="R13" t="n">
-        <v>6992771</v>
+        <v>6992606</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,11 +1902,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1938,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361784</v>
+        <v>123361781</v>
       </c>
       <c r="B14" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1954,21 +1944,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1978,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506806</v>
+        <v>506927</v>
       </c>
       <c r="R14" t="n">
-        <v>6992719</v>
+        <v>6992503</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,6 +2004,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2147,10 +2142,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123361786</v>
+        <v>123361782</v>
       </c>
       <c r="B16" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2163,21 +2158,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2187,10 +2182,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506816</v>
+        <v>506875</v>
       </c>
       <c r="R16" t="n">
-        <v>6992606</v>
+        <v>6992618</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,6 +2218,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361792</v>
+        <v>123361790</v>
       </c>
       <c r="B3" t="n">
         <v>79869</v>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506764</v>
+        <v>506921</v>
       </c>
       <c r="R3" t="n">
-        <v>6992754</v>
+        <v>6992561</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123361788</v>
+        <v>123361783</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507086</v>
+        <v>506764</v>
       </c>
       <c r="R4" t="n">
-        <v>6992321</v>
+        <v>6992771</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,6 +969,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123361793</v>
+        <v>123361782</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506759</v>
+        <v>506875</v>
       </c>
       <c r="R5" t="n">
-        <v>6992756</v>
+        <v>6992618</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,6 +1076,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123361780</v>
+        <v>123361781</v>
       </c>
       <c r="B6" t="n">
         <v>57491</v>
@@ -1137,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506956</v>
+        <v>506927</v>
       </c>
       <c r="R6" t="n">
-        <v>6992441</v>
+        <v>6992503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,7 +1187,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123361778</v>
+        <v>123361779</v>
       </c>
       <c r="B7" t="n">
         <v>57491</v>
@@ -1244,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506992</v>
+        <v>506956</v>
       </c>
       <c r="R7" t="n">
-        <v>6992277</v>
+        <v>6992433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123361784</v>
+        <v>123361778</v>
       </c>
       <c r="B8" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506806</v>
+        <v>506992</v>
       </c>
       <c r="R8" t="n">
-        <v>6992719</v>
+        <v>6992277</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,6 +1397,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,10 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123361783</v>
+        <v>123361785</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,21 +1444,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1453,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506764</v>
+        <v>506757</v>
       </c>
       <c r="R9" t="n">
-        <v>6992771</v>
+        <v>6992768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,11 +1504,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,10 +1530,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361785</v>
+        <v>123361780</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1536,21 +1546,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1560,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506757</v>
+        <v>506956</v>
       </c>
       <c r="R10" t="n">
-        <v>6992768</v>
+        <v>6992441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,6 +1606,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,7 +1637,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123361789</v>
+        <v>123361793</v>
       </c>
       <c r="B11" t="n">
         <v>79869</v>
@@ -1662,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506918</v>
+        <v>506759</v>
       </c>
       <c r="R11" t="n">
-        <v>6992555</v>
+        <v>6992756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1739,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123361790</v>
+        <v>123361788</v>
       </c>
       <c r="B12" t="n">
         <v>79869</v>
@@ -1764,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506921</v>
+        <v>507086</v>
       </c>
       <c r="R12" t="n">
-        <v>6992561</v>
+        <v>6992321</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,10 +1943,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361781</v>
+        <v>123361789</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,21 +1959,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506927</v>
+        <v>506918</v>
       </c>
       <c r="R14" t="n">
-        <v>6992503</v>
+        <v>6992555</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,11 +2019,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2035,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123361779</v>
+        <v>123361784</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,21 +2061,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2075,10 +2085,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506956</v>
+        <v>506806</v>
       </c>
       <c r="R15" t="n">
-        <v>6992433</v>
+        <v>6992719</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,11 +2121,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,10 +2147,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123361782</v>
+        <v>123361792</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,21 +2163,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2182,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506875</v>
+        <v>506764</v>
       </c>
       <c r="R16" t="n">
-        <v>6992618</v>
+        <v>6992754</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,11 +2223,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118356298</v>
+        <v>118356297</v>
       </c>
       <c r="B2" t="n">
-        <v>79572</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506782</v>
+        <v>506726</v>
       </c>
       <c r="R2" t="n">
-        <v>6992742</v>
+        <v>6992743</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123361792</v>
+        <v>118356298</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,20 +814,24 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stor-långtjärnen, Jmt</t>
+          <t>Stor-Långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506764</v>
+        <v>506782</v>
       </c>
       <c r="R3" t="n">
-        <v>6992754</v>
+        <v>6992742</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,27 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Amanda Selinder</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123361793</v>
+        <v>123361784</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506759</v>
+        <v>506806</v>
       </c>
       <c r="R4" t="n">
-        <v>6992756</v>
+        <v>6992719</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,15 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123361790</v>
+        <v>123361785</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506921</v>
+        <v>506757</v>
       </c>
       <c r="R5" t="n">
-        <v>6992561</v>
+        <v>6992768</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,15 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123361785</v>
+        <v>123361786</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1137,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506757</v>
+        <v>506816</v>
       </c>
       <c r="R6" t="n">
-        <v>6992768</v>
+        <v>6992606</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123361779</v>
+        <v>123361788</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,21 +1199,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506956</v>
+        <v>507086</v>
       </c>
       <c r="R7" t="n">
-        <v>6992433</v>
+        <v>6992321</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1259,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123361780</v>
+        <v>123361789</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,21 +1296,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506956</v>
+        <v>506918</v>
       </c>
       <c r="R8" t="n">
-        <v>6992441</v>
+        <v>6992555</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,11 +1356,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,10 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123361783</v>
+        <v>123361790</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506764</v>
+        <v>506921</v>
       </c>
       <c r="R9" t="n">
-        <v>6992771</v>
+        <v>6992561</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,11 +1453,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,15 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123361784</v>
+        <v>123361791</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506806</v>
+        <v>506793</v>
       </c>
       <c r="R10" t="n">
-        <v>6992719</v>
+        <v>6992683</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,15 +1576,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123361788</v>
+        <v>123361792</v>
       </c>
       <c r="B11" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1647,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507086</v>
+        <v>506764</v>
       </c>
       <c r="R11" t="n">
-        <v>6992321</v>
+        <v>6992754</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,15 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123361789</v>
+        <v>123361793</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506918</v>
+        <v>506759</v>
       </c>
       <c r="R12" t="n">
-        <v>6992555</v>
+        <v>6992756</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,15 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123361786</v>
+        <v>123361778</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1827,21 +1781,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506816</v>
+        <v>506992</v>
       </c>
       <c r="R13" t="n">
-        <v>6992606</v>
+        <v>6992277</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,6 +1841,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1913,10 +1872,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123361778</v>
+        <v>123361779</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1948,10 +1907,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506992</v>
+        <v>506956</v>
       </c>
       <c r="R14" t="n">
-        <v>6992277</v>
+        <v>6992433</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,10 +1974,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123361782</v>
+        <v>123361780</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2050,10 +2009,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506875</v>
+        <v>506956</v>
       </c>
       <c r="R15" t="n">
-        <v>6992618</v>
+        <v>6992441</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2120,7 +2079,7 @@
         <v>123361781</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2216,6 +2175,210 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123361782</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>506875</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6992618</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123361783</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stor-långtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>506764</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6992771</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2467-2025 artfynd.xlsx
+++ b/artfynd/A 2467-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118356297</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118356298</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361784</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361785</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361786</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361788</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361789</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361790</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361791</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361792</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361793</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1869,6 +1929,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361778</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1971,6 +2036,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361779</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2073,6 +2143,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361780</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2175,6 +2250,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361781</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2277,6 +2357,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361782</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2379,8 +2464,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123361783</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>